--- a/artfynd/A 42565-2024 artfynd.xlsx
+++ b/artfynd/A 42565-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66490746</v>
+        <v>66490747</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387807.7524862377</v>
+        <v>387835</v>
       </c>
       <c r="R2" t="n">
-        <v>7065781.736494226</v>
+        <v>7065789</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,21 +743,11 @@
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,54 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66490754</v>
+        <v>66490749</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långnäset, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387884.899992076</v>
+        <v>388044</v>
       </c>
       <c r="R3" t="n">
-        <v>7065538.878698454</v>
+        <v>7065817</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,21 +845,11 @@
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -895,7 +861,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,54 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66490751</v>
+        <v>66490750</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långnäset, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388064.85946722</v>
+        <v>388065</v>
       </c>
       <c r="R4" t="n">
-        <v>7065750.862996753</v>
+        <v>7065751</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -990,21 +947,11 @@
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1016,7 +963,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1037,12 +984,7 @@
         <v>66490753</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388064.85946722</v>
+        <v>388065</v>
       </c>
       <c r="R5" t="n">
-        <v>7065750.862996753</v>
+        <v>7065751</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1107,19 +1049,9 @@
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2010-06-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66490748</v>
+        <v>66490745</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,38 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långnäset, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>387834.6826972317</v>
+        <v>387808</v>
       </c>
       <c r="R6" t="n">
-        <v>7065789.212235067</v>
+        <v>7065782</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1228,21 +1151,11 @@
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1254,7 +1167,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1272,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66490749</v>
+        <v>66490746</v>
       </c>
       <c r="B7" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1312,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388044.0897525258</v>
+        <v>387808</v>
       </c>
       <c r="R7" t="n">
-        <v>7065816.841023869</v>
+        <v>7065782</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1345,21 +1253,11 @@
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1371,7 +1269,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1389,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66490750</v>
+        <v>66490748</v>
       </c>
       <c r="B8" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,34 +1298,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långnäset, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388064.85946722</v>
+        <v>387835</v>
       </c>
       <c r="R8" t="n">
-        <v>7065750.862996753</v>
+        <v>7065789</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1462,21 +1359,11 @@
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1488,7 +1375,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1506,50 +1393,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66490745</v>
+        <v>66490751</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långnäset, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387807.7524862377</v>
+        <v>388065</v>
       </c>
       <c r="R9" t="n">
-        <v>7065781.736494226</v>
+        <v>7065751</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1579,21 +1465,11 @@
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1605,7 +1481,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1623,50 +1499,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66490747</v>
+        <v>66490754</v>
       </c>
       <c r="B10" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långnäset, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387834.6826972317</v>
+        <v>387885</v>
       </c>
       <c r="R10" t="n">
-        <v>7065789.212235067</v>
+        <v>7065539</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1696,21 +1571,11 @@
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2010-06-18</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1722,7 +1587,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>6652</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 42565-2024 artfynd.xlsx
+++ b/artfynd/A 42565-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490747</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490749</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490750</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490753</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490745</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490746</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490748</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490751</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,8 +1647,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490754</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>